--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.174613285252886</v>
+        <v>0.3533746588535939</v>
       </c>
       <c r="D2" t="n">
-        <v>1.701920317693714</v>
+        <v>0.2765620516252285</v>
       </c>
       <c r="E2" t="n">
-        <v>1.592805624805421</v>
+        <v>0.2588309140308809</v>
       </c>
       <c r="F2" t="n">
-        <v>2.24103810279815</v>
+        <v>0.3641686917046995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.360224534863727</v>
+        <v>0.8710364869153557</v>
       </c>
       <c r="D3" t="n">
-        <v>6.183996523290014</v>
+        <v>1.004899435034627</v>
       </c>
       <c r="E3" t="n">
-        <v>1.592805624805421</v>
+        <v>0.2588309140308809</v>
       </c>
       <c r="F3" t="n">
-        <v>2.24103810279815</v>
+        <v>0.3641686917046995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
